--- a/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>source_pdf</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>validation_tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,12 +516,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/13/2025</t>
+          <t>01/15/2024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -529,37 +534,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3.300%</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1368</v>
+        <v>12585</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3109458</t>
+          <t>33458134</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>31.000%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-24.600%</t>
+          <t>-15.500%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ALSE-134457261</t>
+          <t>ALSE-133861908</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,12 +579,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134457261/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133861908/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -596,55 +601,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/02/2025</t>
+          <t>07/29/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.400%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.400%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146862</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25658903</t>
+          <t>655639</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.500%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -654,7 +659,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ALSE-134493932</t>
+          <t>ALSE-134133869</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -664,12 +669,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134493932/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134133869/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -681,7 +691,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>07/08/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -701,35 +711,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>448433</t>
+          <t>649737</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5809</v>
+        <v>5233</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14947752</t>
+          <t>14438597</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>13.900%</t>
+          <t>39.000%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>-6.500%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -739,7 +749,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ALSE-134556264</t>
+          <t>ALSE-134137141</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,12 +759,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134556264/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134137141/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -766,22 +781,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>07/01/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -800,21 +815,21 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6015</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18181049</t>
+          <t>26706477</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -824,22 +839,27 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ALSE-134608548</t>
+          <t>ALSE-134145280</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Rates Reviewed and Filed</t>
+          <t>Received and Filed</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134608548/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134145280/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -851,12 +871,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>05/13/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -871,35 +891,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1146061</t>
+          <t>3109458</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>31.000%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-24.600%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -909,7 +929,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ALSE-134649640</t>
+          <t>ALSE-134457261</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -919,12 +939,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134457261/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -936,12 +961,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>06/02/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -974,7 +999,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>972673</t>
+          <t>25658903</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -994,7 +1019,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-134649640</t>
+          <t>ALSE-134493932</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1004,12 +1029,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134493932/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1021,55 +1051,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>448433</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5809</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2365931</t>
+          <t>14947752</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.900%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1079,7 +1109,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134649640</t>
+          <t>ALSE-134556264</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1089,12 +1119,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134556264/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1141,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1121,40 +1156,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>642</v>
+        <v>6015</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>333916</t>
+          <t>18181049</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>45.200%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-10.000%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1164,7 +1199,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134863872</t>
+          <t>ALSE-134608548</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1174,12 +1209,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134863872/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134608548/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1231,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1211,35 +1251,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-178405</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4214</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4955691</t>
+          <t>1146061</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-6.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1249,7 +1289,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GECC-134902175</t>
+          <t>ALSE-134649640</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1259,12 +1299,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1321,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1296,35 +1341,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-25293</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>766450</t>
+          <t>972673</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-5.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1334,7 +1379,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GECC-134902175</t>
+          <t>ALSE-134649640</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1344,12 +1389,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1361,55 +1411,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>289896</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1681</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4828381</t>
+          <t>2365931</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>10.040%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1419,7 +1469,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>LBPM-134778720</t>
+          <t>ALSE-134649640</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1429,12 +1479,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134778720/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1446,55 +1501,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-485</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>642</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>333916</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>45.200%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-11.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1504,7 +1559,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>LBPM-134857087</t>
+          <t>ALSE-134863872</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1514,12 +1569,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134863872/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1591,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/15/2024</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1546,40 +1606,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.800%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-224172</t>
+          <t>103750</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1725</v>
+        <v>6317</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4490217</t>
+          <t>13280890</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>67.900%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-14.000%</t>
+          <t>-18.600%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1589,7 +1649,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>LBPM-134857087</t>
+          <t>GECC-134044604</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1599,12 +1659,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1681,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/15/2024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1631,40 +1696,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.400%</t>
+          <t>0.800%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-17386</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>95</v>
+        <v>1358</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>269668</t>
+          <t>3206345</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>38.700%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-11.200%</t>
+          <t>-13.300%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1674,7 +1739,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>LBPM-134857087</t>
+          <t>GECC-134044604</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1684,12 +1749,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1771,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
+          <t>05/15/2024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1716,40 +1786,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>1380618</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>21035</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>37546933</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>27.200%</t>
+          <t>150.400%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-25.500%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1759,7 +1829,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PRGS-134471019</t>
+          <t>GECC-134044604</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1769,12 +1839,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1861,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
+          <t>05/15/2024</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1801,40 +1876,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>128506</t>
+          <t>348563</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9548</v>
+        <v>4593</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2855688</t>
+          <t>9479421</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31.500%</t>
+          <t>77.500%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-12.500%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1844,7 +1919,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>PRGS-134471019</t>
+          <t>GECC-134044604</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1854,12 +1929,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1951,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1886,40 +1966,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>275429</t>
+          <t>-178405</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>11935</v>
+        <v>4214</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3934700</t>
+          <t>4955691</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>32.200%</t>
+          <t>6.200%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>-6.700%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1929,7 +2009,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PRGS-134471019</t>
+          <t>GECC-134902175</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1939,12 +2019,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1956,12 +2041,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/14/2025</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1971,40 +2056,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>116070</t>
+          <t>-25293</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4170</v>
+        <v>424</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1615112</t>
+          <t>766450</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>37.700%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.900%</t>
+          <t>-5.600%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2014,7 +2099,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>LBPM-134350221</t>
+          <t>GECC-134902175</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2024,12 +2109,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134350221/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2041,55 +2131,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07/19/2025</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-11.900%</t>
+          <t>37.500%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>22.800%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3226494</t>
+          <t>983919</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>33557</v>
+        <v>2438</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>80536341</t>
+          <t>4317467</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-0.400%</t>
+          <t>38.460%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-6.200%</t>
+          <t>4.870%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2099,7 +2189,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LBPM-134543988</t>
+          <t>LBPM-133923055</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2109,12 +2199,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134543988/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133923055/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2126,57 +2221,57 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>37.500%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8.000%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>225</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>41185</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>9.700%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>9302</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>10809278</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>22.800%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-27.700%</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -2184,7 +2279,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SFMA-134293997</t>
+          <t>LBPM-133923055</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2194,12 +2289,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133923055/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2311,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>02/13/2024</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2226,42 +2326,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3.400%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>12</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>26218</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7.300%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>254760</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>176625027</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>33.900%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-29.400%</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -2269,7 +2369,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SFMA-134293997</t>
+          <t>LBPM-133971219</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2279,12 +2379,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2401,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>02/13/2024</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2316,35 +2421,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10.800%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.300%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-42193</t>
+          <t>229353</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10015</v>
+        <v>2284</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15577388</t>
+          <t>5238263</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20.200%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2354,7 +2459,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>SFMA-134310862</t>
+          <t>LBPM-133971219</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2364,12 +2469,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2491,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>02/13/2024</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2401,37 +2511,37 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4.800%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>19535</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>164</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>410942</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>12.500%</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-1.800%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-4710399</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>305575</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>256214819</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>25.200%</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-21.700%</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -2439,7 +2549,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>SFMA-134310862</t>
+          <t>LBPM-133971219</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2449,12 +2559,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2581,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07/15/2025</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2484,32 +2599,37 @@
           <t>04.0005 Other Homeowners</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>19.100%</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-6232</t>
+          <t>289896</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>99778</v>
+        <v>1681</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>165691149</t>
+          <t>4828381</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.400%</t>
+          <t>10.040%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-4.900%</t>
+          <t>4.010%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2519,7 +2639,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>SFMA-134524072</t>
+          <t>LBPM-134778720</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2529,12 +2649,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134524072/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134778720/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2546,75 +2671,2950 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-485</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>11</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>22007</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-11.000%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>LBPM-134857087</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-224172</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1725</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4490217</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-14.000%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>LBPM-134857087</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-6.400%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-17386</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>95</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>269668</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-11.200%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>LBPM-134857087</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>01/12/2024</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>7.300%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6.400%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>368899</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>4891</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5731846</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>25.800%</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>PRGS-133901358</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133901358/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>01/19/2024</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>7.800%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-1.300%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-329</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>28</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>24822</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>6.600%</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>PRGS-133927798</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>01/19/2024</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.900%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3.600%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1833723</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>61301</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>51427070</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>11.000%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>PRGS-133927798</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>01/19/2024</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>7.800%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>7.000%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3777707</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>47339</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>54075561</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>21.000%</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-7.000%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>PRGS-133927798</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>01/19/2024</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Progressive Specialty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7.800%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.700%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>81</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>101454</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>PRGS-133927798</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>6.800%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>27.200%</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>PRGS-134471019</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>128506</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>9548</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2855688</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>PRGS-134471019</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>7.000%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>275429</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>11935</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3934700</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>32.200%</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>PRGS-134471019</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>04/22/2024</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>26.500%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>24.000%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>15331608</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>26143</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>63815244</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>25.500%</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>11.600%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>LBPM-133909702</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133909702/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>05/14/2024</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>26.900%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>26.900%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>431551</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>4689</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1606934</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>39.200%</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-6.200%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>LBPM-133961937</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133961937/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10/23/2024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>13.000%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10072018</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>32028</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77521057</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>43.400%</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>LBPM-134101230</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134101230/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11/09/2024</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>13.700%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2828011</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>39502</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>93420150</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>9.000%</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>rate_change_withdrawn</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>LBPM-134141511</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134141511/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>09/30/2024</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>12.200%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>7.400%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>280735</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3783991</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>38.400%</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3.200%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>LBPM-134228709</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134228709/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>05/14/2025</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7.200%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7.200%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>116070</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>4170</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1615112</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>37.700%</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-0.900%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>LBPM-134350221</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134350221/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>07/19/2025</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-11.900%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-4.000%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-3226494</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>33557</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>80536341</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>-0.400%</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-6.200%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>LBPM-134543988</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134543988/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>01/15/2024</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>14.000%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8.700%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>10038139</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>92265</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>115804490</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>38.800%</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-46.300%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SFMA-133900830</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133900830/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>22.000%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8.600%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1162482</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>9349</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>13490184</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>24.200%</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-0.900%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>SFMA-134000554</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134000554/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>7.200%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11675136</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>294447</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>234090658</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>23.400%</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-4.900%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>SFMA-134000554</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134000554/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>07/01/2024</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-0.100%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-5397</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>4080</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>4120710</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-7.600%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>SFMA-134074421</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134074421/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>08/01/2024</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>442</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>196561</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>10.500%</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-8.300%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SFMA-134075954</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134075954/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>08/01/2024</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>6662</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1456069</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>10.900%</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-10.400%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SFMA-134075954</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134075954/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10/15/2024</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>11.500%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>13774377</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>96178</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>137540966</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>24.000%</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>SFMA-134217410</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134217410/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>9302</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>10809278</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>22.800%</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-27.700%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SFMA-134293997</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>254760</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>176625027</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>33.900%</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-29.400%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SFMA-134293997</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10.800%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-0.300%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-42193</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>10015</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>15577388</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20.200%</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-13.500%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>SFMA-134310862</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-1.800%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-4710399</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>305575</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>256214819</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>25.200%</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-21.700%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>SFMA-134310862</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>07/15/2025</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-6232</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>99778</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>165691149</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3.400%</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-4.900%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>SFMA-134524072</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134524072/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>04/05/2024</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>20461</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>36236588</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>30.200%</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-3.100%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>TRVD-134030789</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134030789/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10/04/2024</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>13.200%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>12.400%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>4650901</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>21070</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>37507270</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>28.200%</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>TRVD-G134243122</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134248861/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>02/15/2026</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I58" t="n">
         <v>20583</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>43950044</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>TRVD-G134776712</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Rates Reviewed and Filed</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>2025-12-19</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>output/pdfs/MT/134780245/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R58"/>
+  <dimension ref="A1:T58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -592,6 +602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -682,6 +702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -772,6 +802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -862,6 +902,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -949,7 +999,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1099,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1199,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1299,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1399,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1499,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1599,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1699,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1672,6 +1802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1762,6 +1902,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1852,6 +2002,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1942,6 +2102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2029,7 +2199,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2299,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2212,6 +2402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2302,6 +2502,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2392,6 +2602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2482,6 +2702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2572,6 +2802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2659,7 +2899,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2999,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2839,7 +3099,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2929,7 +3199,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3022,6 +3302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3112,6 +3402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3202,6 +3502,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3292,6 +3602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3382,6 +3702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3469,7 +3799,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3899,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3999,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3742,6 +4102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3832,6 +4202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3922,6 +4302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4012,6 +4402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4102,6 +4502,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4189,7 +4599,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4699,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4372,6 +4802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4462,6 +4902,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4552,6 +5002,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4642,6 +5102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4732,6 +5202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4822,6 +5302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4912,6 +5402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4999,7 +5499,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5599,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5699,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5799,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5894,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5442,6 +5992,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5532,6 +6092,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5614,7 +6184,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T58"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -609,9 +614,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -709,9 +715,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -809,9 +816,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -909,9 +917,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -999,7 +1008,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1009,7 +1018,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1113,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1109,7 +1123,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1218,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1209,7 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -1309,9 +1333,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1409,9 +1434,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1509,9 +1535,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1609,9 +1636,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1699,7 +1727,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1709,7 +1737,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -1809,9 +1842,10 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1909,9 +1943,10 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2009,9 +2044,10 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2109,9 +2145,10 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2199,7 +2236,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2209,7 +2246,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2341,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2309,7 +2351,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2409,9 +2456,10 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2509,9 +2557,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2609,9 +2658,10 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2709,9 +2759,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2809,9 +2860,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2899,7 +2951,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2909,7 +2961,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3056,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3009,7 +3066,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3161,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3109,7 +3171,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3266,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3209,7 +3276,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3309,9 +3381,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3409,9 +3482,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3509,9 +3583,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3609,9 +3684,10 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3709,9 +3785,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3799,7 +3876,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3809,7 +3886,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3981,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3909,7 +3991,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4086,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4009,7 +4096,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -4109,9 +4201,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4209,9 +4302,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4309,9 +4403,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4409,9 +4504,10 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4509,9 +4605,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4599,7 +4696,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4609,7 +4706,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4801,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4709,7 +4811,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -4809,9 +4916,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4909,9 +5017,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5009,9 +5118,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5109,9 +5219,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5209,9 +5320,10 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5309,9 +5421,10 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5409,9 +5522,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5499,7 +5613,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5509,7 +5623,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5718,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5609,7 +5728,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5823,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5709,7 +5833,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5928,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -5809,7 +5938,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5904,9 +6038,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5999,9 +6134,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6099,9 +6235,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6194,9 +6331,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
@@ -6028,7 +6028,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6038,10 +6038,14 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,7 +627,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/29/2024</t>
+          <t>12/18/2023</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -637,45 +637,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.400%</t>
+          <t>28.400%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22.400%</t>
+          <t>28.400%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>146862</t>
+          <t>644317</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>505</v>
+        <v>1404</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>655639</t>
+          <t>2268722</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24.500%</t>
+          <t>67.400%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ALSE-134133869</t>
+          <t>ALSE-133893762</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134133869/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133893762/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07/08/2024</t>
+          <t>07/29/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -743,40 +743,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>22.400%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>22.400%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>649737</t>
+          <t>146862</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5233</v>
+        <v>505</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14438597</t>
+          <t>655639</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>39.000%</t>
+          <t>24.500%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-6.500%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ALSE-134137141</t>
+          <t>ALSE-134133869</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134137141/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134133869/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -829,55 +829,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07/01/2024</t>
+          <t>07/08/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>649737</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5233</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26706477</t>
+          <t>14438597</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>39.000%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-6.500%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -887,22 +887,22 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ALSE-134145280</t>
+          <t>ALSE-134137141</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Received and Filed</t>
+          <t>Rates Reviewed and Filed</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134145280/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134137141/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/13/2025</t>
+          <t>07/01/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -950,35 +950,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1368</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3109458</t>
+          <t>26706477</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-24.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -988,44 +988,40 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ALSE-134457261</t>
+          <t>ALSE-134145280</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Rates Reviewed and Filed</t>
+          <t>Received and Filed</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134457261/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134145280/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1035,12 +1031,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/02/2025</t>
+          <t>05/13/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1055,35 +1051,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25658903</t>
+          <t>3109458</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>31.000%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-24.600%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1093,7 +1089,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-134493932</t>
+          <t>ALSE-134457261</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,17 +1099,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134493932/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134457261/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1123,14 +1119,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1140,55 +1132,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>06/02/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>448433</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5809</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14947752</t>
+          <t>25658903</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1198,7 +1190,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134556264</t>
+          <t>ALSE-134493932</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1208,17 +1200,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134556264/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134493932/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1228,14 +1220,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1245,7 +1233,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1265,35 +1253,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>448433</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6015</v>
+        <v>5809</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18181049</t>
+          <t>14947752</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>13.900%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1303,7 +1291,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134608548</t>
+          <t>ALSE-134556264</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1313,12 +1301,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134608548/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134556264/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1346,22 +1334,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1380,21 +1368,21 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>6015</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1146061</t>
+          <t>18181049</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-10.000%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1404,7 +1392,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134649640</t>
+          <t>ALSE-134608548</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1414,12 +1402,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134608548/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1452,7 +1440,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1485,7 +1473,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>972673</t>
+          <t>1146061</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1553,7 +1541,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1586,7 +1574,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2365931</t>
+          <t>972673</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1649,50 +1637,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>333916</t>
+          <t>2365931</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>45.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1707,7 +1695,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134863872</t>
+          <t>ALSE-134649640</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1717,17 +1705,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134863872/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1737,14 +1725,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1754,55 +1738,55 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/15/2024</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>103750</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6317</v>
+        <v>696</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13280890</t>
+          <t>1554850</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>67.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-18.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1812,7 +1796,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>GECC-134044604</t>
+          <t>ALSE-134857330</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1822,12 +1806,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134857330/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1837,12 +1821,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1855,55 +1839,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/15/2024</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.800%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1358</v>
+        <v>642</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3206345</t>
+          <t>333916</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>38.700%</t>
+          <t>45.200%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-13.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1913,7 +1897,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>GECC-134044604</t>
+          <t>ALSE-134863872</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1923,12 +1907,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134863872/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1938,12 +1922,12 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1956,55 +1940,55 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/15/2024</t>
+          <t>05/21/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1380618</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>21035</v>
+        <v>2578</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>37546933</t>
+          <t>345659</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>150.400%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-25.500%</t>
+          <t>-1.500%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2014,7 +1998,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GECC-134044604</t>
+          <t>ALSE-134896033</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2024,12 +2008,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134896033/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2039,12 +2023,12 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -2062,7 +2046,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2077,35 +2061,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>0.800%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>348563</t>
+          <t>103750</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4593</v>
+        <v>6317</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9479421</t>
+          <t>13280890</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>77.500%</t>
+          <t>67.900%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-12.500%</t>
+          <t>-18.600%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2158,12 +2142,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/15/2024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2178,35 +2162,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>0.800%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-178405</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4214</v>
+        <v>1358</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4955691</t>
+          <t>3206345</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6.200%</t>
+          <t>38.700%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-6.700%</t>
+          <t>-13.300%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2216,7 +2200,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>GECC-134902175</t>
+          <t>GECC-134044604</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2226,34 +2210,30 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2263,12 +2243,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/15/2024</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2283,35 +2263,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.900%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-25293</t>
+          <t>1380618</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>424</v>
+        <v>21035</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>766450</t>
+          <t>37546933</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>150.400%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-5.600%</t>
+          <t>-25.500%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2321,7 +2301,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GECC-134902175</t>
+          <t>GECC-134044604</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2331,34 +2311,30 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2368,55 +2344,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>02/01/2024</t>
+          <t>05/15/2024</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>37.500%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22.800%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>983919</t>
+          <t>348563</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2438</v>
+        <v>4593</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4317467</t>
+          <t>9479421</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>38.460%</t>
+          <t>77.500%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4.870%</t>
+          <t>-12.500%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2426,7 +2402,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LBPM-133923055</t>
+          <t>GECC-134044604</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2436,12 +2412,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133923055/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134044604/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2469,55 +2445,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>02/01/2024</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37.500%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>-178405</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>225</v>
+        <v>4214</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>4955691</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>6.200%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-6.700%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2527,7 +2503,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>LBPM-133923055</t>
+          <t>GECC-134902175</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2537,12 +2513,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133923055/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2552,12 +2528,12 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2570,12 +2546,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>02/13/2024</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2585,40 +2561,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.400%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>-25293</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>424</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>766450</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.600%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2628,7 +2604,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>LBPM-133971219</t>
+          <t>GECC-134902175</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2638,12 +2614,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2653,12 +2629,12 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2671,7 +2647,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>02/13/2024</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2681,45 +2657,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>37.500%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>22.800%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>229353</t>
+          <t>983919</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2284</v>
+        <v>2438</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5238263</t>
+          <t>4317467</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>38.460%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.870%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2729,7 +2705,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>LBPM-133971219</t>
+          <t>LBPM-133923055</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2739,12 +2715,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133923055/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2772,50 +2748,50 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>02/13/2024</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>37.500%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19535</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>410942</t>
+          <t>41185</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2830,7 +2806,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>LBPM-133971219</t>
+          <t>LBPM-133923055</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2840,12 +2816,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133923055/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2873,55 +2849,55 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/13/2024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>3.400%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>289896</t>
+          <t>902</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1681</v>
+        <v>12</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4828381</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>10.040%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2931,7 +2907,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>LBPM-134778720</t>
+          <t>LBPM-133971219</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2941,34 +2917,30 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134778720/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2978,12 +2950,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>02/13/2024</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2998,35 +2970,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-485</t>
+          <t>229353</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>2284</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>5238263</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-11.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3036,7 +3008,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>LBPM-134857087</t>
+          <t>LBPM-133971219</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3046,34 +3018,30 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3083,12 +3051,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>02/13/2024</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3103,35 +3071,35 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-224172</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1725</v>
+        <v>164</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4490217</t>
+          <t>410942</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-14.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3141,7 +3109,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>LBPM-134857087</t>
+          <t>LBPM-133971219</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3151,34 +3119,30 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133971219/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3188,55 +3152,55 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>19.100%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.400%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-17386</t>
+          <t>289896</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>95</v>
+        <v>1681</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>269668</t>
+          <t>4828381</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>10.040%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-11.200%</t>
+          <t>4.010%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3246,7 +3210,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>LBPM-134857087</t>
+          <t>LBPM-134778720</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3256,17 +3220,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134778720/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3276,14 +3240,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3293,12 +3253,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01/12/2024</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3308,40 +3268,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>-9.500%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.400%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>368899</t>
+          <t>-485</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4891</v>
+        <v>11</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5731846</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.000%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3351,7 +3311,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>PRGS-133901358</t>
+          <t>LBPM-134857087</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3361,12 +3321,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133901358/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3376,12 +3336,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -3394,12 +3354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01/19/2024</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3409,40 +3369,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.800%</t>
+          <t>-9.500%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-329</t>
+          <t>-224172</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>1725</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>4490217</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6.600%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.000%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3452,7 +3412,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>PRGS-133927798</t>
+          <t>LBPM-134857087</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3462,12 +3422,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3477,12 +3437,12 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -3495,12 +3455,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01/19/2024</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3510,40 +3470,40 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3.900%</t>
+          <t>-9.500%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>-6.400%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1833723</t>
+          <t>-17386</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>61301</v>
+        <v>95</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>51427070</t>
+          <t>269668</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-11.200%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3553,7 +3513,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>PRGS-133927798</t>
+          <t>LBPM-134857087</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3563,12 +3523,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3578,12 +3538,12 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -3596,12 +3556,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01/19/2024</t>
+          <t>01/12/2024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3611,40 +3571,40 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.800%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>6.400%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3777707</t>
+          <t>368899</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>47339</v>
+        <v>4891</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>54075561</t>
+          <t>5731846</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3654,7 +3614,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>PRGS-133927798</t>
+          <t>PRGS-133901358</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3664,12 +3624,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133901358/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3702,7 +3662,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3722,25 +3682,25 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.700%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>-329</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>6.600%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3798,12 +3758,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
+          <t>01/19/2024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3813,40 +3773,40 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>3.900%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>1833723</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>9</v>
+        <v>61301</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>51427070</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>27.200%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3856,7 +3816,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>PRGS-134471019</t>
+          <t>PRGS-133927798</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3866,34 +3826,30 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3903,12 +3859,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
+          <t>01/19/2024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3918,40 +3874,40 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>7.800%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>128506</t>
+          <t>3777707</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9548</v>
+        <v>47339</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2855688</t>
+          <t>54075561</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31.500%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3961,7 +3917,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>PRGS-134471019</t>
+          <t>PRGS-133927798</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3971,34 +3927,30 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4008,12 +3960,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
+          <t>01/19/2024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4023,40 +3975,40 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>7.800%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>0.700%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>275429</t>
+          <t>752</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>11935</v>
+        <v>81</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3934700</t>
+          <t>101454</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>32.200%</t>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4066,7 +4018,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>PRGS-134471019</t>
+          <t>PRGS-133927798</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4076,34 +4028,30 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133927798/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4113,55 +4061,55 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04/22/2024</t>
+          <t>06/06/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>26.500%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24.000%</t>
+          <t>6.800%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15331608</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>26143</v>
+        <v>9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>63815244</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>25.500%</t>
+          <t>27.200%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>11.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4171,7 +4119,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>LBPM-133909702</t>
+          <t>PRGS-134471019</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4181,12 +4129,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133909702/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4196,12 +4144,12 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
@@ -4214,12 +4162,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>05/14/2024</t>
+          <t>06/06/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4234,35 +4182,35 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>26.900%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>26.900%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>431551</t>
+          <t>128506</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4689</v>
+        <v>9548</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1606934</t>
+          <t>2855688</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>39.200%</t>
+          <t>31.500%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-6.200%</t>
+          <t>-2.500%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4272,7 +4220,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>LBPM-133961937</t>
+          <t>PRGS-134471019</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4282,12 +4230,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133961937/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4297,12 +4245,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
@@ -4315,55 +4263,55 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/23/2024</t>
+          <t>06/06/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10072018</t>
+          <t>275429</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>32028</v>
+        <v>11935</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77521057</t>
+          <t>3934700</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>43.400%</t>
+          <t>32.200%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.900%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4373,7 +4321,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>LBPM-134101230</t>
+          <t>PRGS-134471019</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4383,12 +4331,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134101230/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4398,12 +4346,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U39" t="inlineStr"/>
@@ -4416,80 +4364,80 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/09/2024</t>
+          <t>04/22/2024</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>26.500%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>24.000%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2828011</t>
+          <t>15331608</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>39502</v>
+        <v>26143</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>93420150</t>
+          <t>63815244</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>9.000%</t>
+          <t>25.500%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.600%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>LBPM-134141511</t>
+          <t>LBPM-133909702</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Rates Reviewed and Filed</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134141511/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133909702/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4517,7 +4465,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>09/30/2024</t>
+          <t>05/14/2024</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4532,40 +4480,40 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12.200%</t>
+          <t>26.900%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>26.900%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>280735</t>
+          <t>431551</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1980</v>
+        <v>4689</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3783991</t>
+          <t>1606934</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>38.400%</t>
+          <t>39.200%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>-6.200%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4575,7 +4523,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>LBPM-134228709</t>
+          <t>LBPM-133961937</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4585,12 +4533,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134228709/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133961937/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4618,55 +4566,55 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>05/14/2025</t>
+          <t>10/23/2024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>13.300%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>13.000%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>116070</t>
+          <t>10072018</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4170</v>
+        <v>32028</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1615112</t>
+          <t>77521057</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>37.700%</t>
+          <t>43.400%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4676,7 +4624,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>LBPM-134350221</t>
+          <t>LBPM-134101230</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4686,34 +4634,30 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134350221/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134101230/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4723,7 +4667,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07/19/2025</t>
+          <t>11/09/2024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4743,82 +4687,78 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-11.900%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-3226494</t>
+          <t>2828011</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>33557</v>
+        <v>39502</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>80536341</t>
+          <t>93420150</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-0.400%</t>
+          <t>9.000%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-6.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LBPM-134543988</t>
+          <t>LBPM-134141511</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Rates Reviewed and Filed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134543988/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134141511/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4828,55 +4768,55 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01/15/2024</t>
+          <t>09/30/2024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>14.000%</t>
+          <t>12.200%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10038139</t>
+          <t>280735</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>92265</v>
+        <v>1980</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>115804490</t>
+          <t>3783991</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>38.800%</t>
+          <t>38.400%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-46.300%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4886,7 +4826,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>SFMA-133900830</t>
+          <t>LBPM-134228709</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4896,12 +4836,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/133900830/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134228709/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4929,12 +4869,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>05/14/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4944,35 +4884,35 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>22.000%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8.600%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1162482</t>
+          <t>116070</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9349</v>
+        <v>4170</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>13490184</t>
+          <t>1615112</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24.200%</t>
+          <t>37.700%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4987,7 +4927,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134000554</t>
+          <t>LBPM-134350221</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4997,12 +4937,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134000554/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134350221/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5012,12 +4952,12 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
@@ -5030,12 +4970,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>07/19/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5050,35 +4990,35 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>-11.900%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11675136</t>
+          <t>-3226494</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>294447</v>
+        <v>33557</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>234090658</t>
+          <t>80536341</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23.400%</t>
+          <t>-0.400%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-4.900%</t>
+          <t>-6.200%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5088,7 +5028,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>SFMA-134000554</t>
+          <t>LBPM-134543988</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -5098,12 +5038,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134000554/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134543988/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5113,12 +5053,12 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
@@ -5131,7 +5071,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>07/01/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5141,12 +5081,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5156,30 +5096,30 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-5397</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4080</v>
+        <v>8192</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4120710</t>
+          <t>10966860</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>21.500%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-7.600%</t>
+          <t>-21.100%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5189,7 +5129,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134074421</t>
+          <t>SFMA-133814011</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5199,12 +5139,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134074421/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133814011/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5232,12 +5172,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5247,7 +5187,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5266,21 +5206,21 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>442</v>
+        <v>238445</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>196561</t>
+          <t>182777930</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>10.500%</t>
+          <t>28.500%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-8.300%</t>
+          <t>-25.300%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5290,7 +5230,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>SFMA-134075954</t>
+          <t>SFMA-133814011</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5300,12 +5240,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134075954/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133814011/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5333,55 +5273,55 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>01/15/2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>14.000%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10038139</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6662</v>
+        <v>92265</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1456069</t>
+          <t>115804490</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>38.800%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-10.400%</t>
+          <t>-46.300%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5391,7 +5331,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>SFMA-134075954</t>
+          <t>SFMA-133900830</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5401,12 +5341,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134075954/filing_summary.pdf</t>
+          <t>output/pdfs/MT/133900830/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5434,7 +5374,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/15/2024</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5444,45 +5384,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>11.500%</t>
+          <t>22.000%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>8.600%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>13774377</t>
+          <t>1162482</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>96178</v>
+        <v>9349</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>137540966</t>
+          <t>13490184</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>24.000%</t>
+          <t>24.200%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.900%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5492,7 +5432,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>SFMA-134217410</t>
+          <t>SFMA-134000554</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5502,12 +5442,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134217410/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134000554/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5535,12 +5475,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5550,40 +5490,40 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11675136</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9302</v>
+        <v>294447</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>10809278</t>
+          <t>234090658</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22.800%</t>
+          <t>23.400%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-27.700%</t>
+          <t>-4.900%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5593,7 +5533,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>SFMA-134293997</t>
+          <t>SFMA-134000554</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5603,34 +5543,30 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134000554/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5640,22 +5576,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>07/01/2024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5665,30 +5601,30 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.100%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5397</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>254760</v>
+        <v>4080</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>176625027</t>
+          <t>4120710</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>33.900%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-29.400%</t>
+          <t>-7.600%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5698,7 +5634,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>SFMA-134293997</t>
+          <t>SFMA-134074421</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5708,34 +5644,30 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134074421/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5745,7 +5677,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5760,40 +5692,40 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-0.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-42193</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10015</v>
+        <v>442</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>15577388</t>
+          <t>196561</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>20.200%</t>
+          <t>10.500%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-13.500%</t>
+          <t>-8.300%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5803,7 +5735,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>SFMA-134310862</t>
+          <t>SFMA-134075954</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5813,34 +5745,30 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134075954/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5850,7 +5778,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5865,7 +5793,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5875,30 +5803,30 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-1.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-4710399</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>305575</v>
+        <v>6662</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>256214819</t>
+          <t>1456069</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>25.200%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-21.700%</t>
+          <t>-10.400%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5908,7 +5836,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>SFMA-134310862</t>
+          <t>SFMA-134075954</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5918,34 +5846,30 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134075954/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5955,7 +5879,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07/15/2025</t>
+          <t>10/15/2024</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5973,34 +5897,39 @@
           <t>04.0005 Other Homeowners</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>11.500%</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>13774377</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>96178</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>137540966</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>24.000%</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>-6232</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>99778</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>165691149</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>3.400%</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-4.900%</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -6008,7 +5937,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>SFMA-134524072</t>
+          <t>SFMA-134217410</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -6018,34 +5947,30 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134524072/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134217410/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6055,22 +5980,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>04/05/2024</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6084,21 +6014,21 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>20461</v>
+        <v>9302</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>36236588</t>
+          <t>10809278</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>30.200%</t>
+          <t>22.800%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-3.100%</t>
+          <t>-27.700%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6108,7 +6038,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>TRVD-134030789</t>
+          <t>SFMA-134293997</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -6118,12 +6048,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134030789/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6133,12 +6063,12 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
@@ -6151,55 +6081,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/04/2024</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>12.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4650901</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>21070</v>
+        <v>254760</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>37507270</t>
+          <t>176625027</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>28.200%</t>
+          <t>33.900%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-29.400%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6209,7 +6139,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>TRVD-G134243122</t>
+          <t>SFMA-134293997</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6219,12 +6149,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/MT/134248861/filing_summary.pdf</t>
+          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6234,12 +6164,12 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -6252,93 +6182,689 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>10.800%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-0.300%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-42193</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>10015</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>15577388</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>20.200%</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-13.500%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>SFMA-134310862</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-1.800%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-4710399</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>305575</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>256214819</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>25.200%</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-21.700%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SFMA-134310862</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>07/15/2025</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-6232</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>99778</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>165691149</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>3.400%</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-4.900%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SFMA-134524072</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134524072/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12/15/2023</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>21.500%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>17.900%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>4848121</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>19062</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>27084475</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>221.000%</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-20.300%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>TRVD-133882367</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/133882367/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>04/05/2024</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>20461</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>36236588</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>30.200%</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-3.100%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>TRVD-134030789</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134030789/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10/04/2024</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>13.200%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>12.400%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>4650901</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>21070</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>37507270</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>28.200%</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>TRVD-G134243122</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134248861/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>02/15/2026</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="I64" t="n">
         <v>20583</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>43950044</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>TRVD-G134776712</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Rates Reviewed and Filed</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>2025-12-19</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>output/pdfs/MT/134780245/filing_summary.pdf</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>pipeline_only</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>original</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/mt_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U64"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6865,6 +6865,1618 @@
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>8224</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>12958908</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>21.600%</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-17.300%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>SFMA-134834427</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134834427/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>262721</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>246250631</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>18.500%</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-17.400%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SFMA-134834427</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134834427/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>68.600%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>9.600%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>16874930</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>101799</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>175596220</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>69.300%</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-2.800%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SFMA-134919009</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134919009/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>20915012</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ALSE-134917441</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134917441/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>08/31/2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>19.600%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>19.600%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>175263</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>541</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>894550</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>21.300%</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ALSE-135008553</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135008553/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>16.500%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>47898</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>378</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>798306</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>6.300%</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>ALSE-135032520</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135032520/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>3614</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>8275254</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ALSE-134955783</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134955783/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>16.500%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>118899</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>730</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1981652</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>6.300%</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>ALSE-135032450</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135032450/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Allstate Vehicle and Property Insurance Company</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>27.900%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1103255</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>5601</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>18387581</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>27.500%</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-15.100%</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ALSE-135032575</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135032575/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>7.300%</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>3479619</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>17868</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>58115133</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>6.300%</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1.200%</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>LBPM-135014031</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135014031/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Farmers Direct Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>389</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1058229</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>FAIG-135024104</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135024104/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Farmers Direct Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>921</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>3378875</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>FAIG-135024165</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135024165/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>01/10/2027</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>3743</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>9472316</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>175.000%</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-73.000%</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>USAA-134977077</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134981855/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>01/10/2027</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>6554</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>22398575</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>174.000%</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-75.000%</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>USAA-134977077</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134981855/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>01/10/2027</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>5934</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>15930270</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>174.000%</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-73.000%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>USAA-134977077</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134981855/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>01/10/2027</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>8942</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>30220050</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>146.000%</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-78.000%</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>USAA-134977077</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134981855/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Mid-Century Insurance Company</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1.000%</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-956</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>13492</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>29480739</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>10.100%</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-10.200%</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>FARM-135011632</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/135011632/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
